--- a/data/trans_dic/P16A_n_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A_n_R2-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,09</t>
+          <t>1,34; 4,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,36; 7,69</t>
+          <t>3,46; 7,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 6,11</t>
+          <t>2,18; 6,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,39; 14,69</t>
+          <t>4,6; 14,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,52; 14,33</t>
+          <t>8,47; 13,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,03; 20,2</t>
+          <t>12,55; 19,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,28; 14,37</t>
+          <t>7,86; 14,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,52; 19,97</t>
+          <t>9,18; 19,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,2; 8,27</t>
+          <t>5,19; 8,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,56; 12,73</t>
+          <t>8,55; 12,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,71; 9,24</t>
+          <t>5,56; 9,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,77; 14,88</t>
+          <t>7,77; 15,47</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,3</t>
+          <t>2,52; 5,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,67; 12,17</t>
+          <t>7,52; 12,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,65; 10,15</t>
+          <t>5,63; 10,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,54; 16,83</t>
+          <t>8,51; 17,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,48; 17,3</t>
+          <t>11,47; 17,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,97; 23,79</t>
+          <t>17,06; 24,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,94; 18,15</t>
+          <t>12,11; 17,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,15; 21,11</t>
+          <t>10,14; 20,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,97; 10,23</t>
+          <t>7,02; 10,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,8; 16,63</t>
+          <t>12,76; 16,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,37; 13,07</t>
+          <t>9,58; 13,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,86; 17,5</t>
+          <t>11,01; 17,47</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,43; 10,63</t>
+          <t>6,36; 10,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,03; 15,33</t>
+          <t>10,25; 15,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,86; 12,64</t>
+          <t>7,88; 12,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,8; 18,26</t>
+          <t>11,51; 17,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,85; 17,62</t>
+          <t>12,17; 17,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,92; 27,36</t>
+          <t>20,81; 27,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,83; 20,45</t>
+          <t>14,58; 20,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,97; 24,13</t>
+          <t>15,07; 23,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,85; 13,23</t>
+          <t>9,88; 13,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,66; 20,83</t>
+          <t>16,58; 20,76</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,84; 15,8</t>
+          <t>12,09; 15,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,75; 19,93</t>
+          <t>15,0; 19,81</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,38; 18,83</t>
+          <t>12,47; 18,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,66; 21,23</t>
+          <t>14,46; 21,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,03; 22,73</t>
+          <t>16,02; 22,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,44; 27,84</t>
+          <t>8,82; 28,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,03; 27,16</t>
+          <t>19,66; 27,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,06; 37,17</t>
+          <t>29,2; 37,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,73; 31,09</t>
+          <t>23,49; 30,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,67; 36,26</t>
+          <t>27,78; 36,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,69; 21,89</t>
+          <t>16,87; 22,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,8; 27,79</t>
+          <t>22,83; 28,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,13; 25,95</t>
+          <t>20,73; 25,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,65; 31,07</t>
+          <t>15,79; 31,15</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>29,27; 38,75</t>
+          <t>29,19; 38,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36,12; 45,62</t>
+          <t>35,99; 45,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,04; 39,33</t>
+          <t>30,42; 39,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38,37; 46,62</t>
+          <t>38,68; 46,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>39,31; 49,15</t>
+          <t>39,43; 49,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,55; 61,3</t>
+          <t>51,81; 61,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,51; 57,46</t>
+          <t>47,6; 57,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>48,64; 55,01</t>
+          <t>48,35; 55,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>35,86; 42,75</t>
+          <t>35,96; 42,61</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45,36; 52,43</t>
+          <t>45,35; 52,11</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40,26; 47,35</t>
+          <t>40,58; 47,36</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>44,07; 49,26</t>
+          <t>44,28; 49,42</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38,52; 50,23</t>
+          <t>39,46; 50,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60,35; 71,6</t>
+          <t>60,37; 71,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46,73; 58,06</t>
+          <t>46,8; 57,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48,66; 56,91</t>
+          <t>48,77; 57,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>59,95; 69,41</t>
+          <t>60,09; 69,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>69,0; 78,56</t>
+          <t>68,51; 78,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59,59; 69,19</t>
+          <t>59,65; 69,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>65,75; 91,05</t>
+          <t>65,48; 89,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52,1; 59,57</t>
+          <t>51,95; 59,24</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>66,74; 74,13</t>
+          <t>66,7; 73,81</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54,9; 62,43</t>
+          <t>55,02; 62,49</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>59,58; 82,55</t>
+          <t>59,5; 83,0</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>58,75; 72,03</t>
+          <t>59,18; 72,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>74,19; 84,67</t>
+          <t>74,23; 85,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66,32; 76,65</t>
+          <t>66,71; 76,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63,98; 72,67</t>
+          <t>63,53; 72,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>67,59; 77,83</t>
+          <t>68,31; 78,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,69; 90,6</t>
+          <t>83,92; 90,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,14; 82,11</t>
+          <t>73,35; 82,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>78,42; 83,91</t>
+          <t>78,32; 83,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>66,14; 74,34</t>
+          <t>66,62; 73,99</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>80,9; 87,01</t>
+          <t>81,33; 87,52</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71,74; 78,7</t>
+          <t>71,8; 78,57</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73,36; 78,27</t>
+          <t>73,48; 78,45</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,13; 18,69</t>
+          <t>16,14; 18,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23,8; 26,85</t>
+          <t>23,74; 26,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21,53; 24,43</t>
+          <t>21,45; 24,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22,24; 30,57</t>
+          <t>21,35; 30,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>28,15; 31,49</t>
+          <t>28,34; 31,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,38; 41,67</t>
+          <t>38,35; 41,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,07; 36,39</t>
+          <t>33,27; 36,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>38,68; 54,3</t>
+          <t>38,62; 53,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>22,7; 24,77</t>
+          <t>22,67; 24,75</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31,64; 34,01</t>
+          <t>31,68; 33,94</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27,92; 30,15</t>
+          <t>27,81; 30,07</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>32,06; 41,87</t>
+          <t>32,31; 40,9</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6703; 20208</t>
+          <t>6628; 20032</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15239; 34908</t>
+          <t>15714; 35045</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9233; 25630</t>
+          <t>9141; 27046</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17571; 58754</t>
+          <t>18397; 58586</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>39848; 67008</t>
+          <t>39583; 64615</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>56043; 86928</t>
+          <t>54015; 84536</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32759; 56858</t>
+          <t>31096; 58628</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26685; 62559</t>
+          <t>28744; 60751</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>49961; 79528</t>
+          <t>49922; 80690</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>75692; 112586</t>
+          <t>75632; 111273</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46580; 75339</t>
+          <t>45294; 77087</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>55436; 106108</t>
+          <t>55393; 110336</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18627; 38997</t>
+          <t>18568; 39367</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52733; 83613</t>
+          <t>51689; 83771</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33383; 59959</t>
+          <t>33234; 62085</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36178; 71287</t>
+          <t>36045; 72164</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>71803; 108181</t>
+          <t>71755; 108931</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>103565; 145205</t>
+          <t>104118; 148224</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>67302; 102275</t>
+          <t>68272; 100801</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51964; 108110</t>
+          <t>51919; 106845</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>94895; 139237</t>
+          <t>95597; 136149</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>166113; 215790</t>
+          <t>165491; 218484</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>108176; 150822</t>
+          <t>110589; 151601</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>101651; 163770</t>
+          <t>103010; 163451</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>41088; 67906</t>
+          <t>40612; 68498</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>68373; 104528</t>
+          <t>69890; 105011</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52577; 84574</t>
+          <t>52746; 84917</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63305; 97915</t>
+          <t>61738; 93690</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>81720; 121554</t>
+          <t>83936; 119577</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>148706; 194482</t>
+          <t>147910; 195121</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98081; 135278</t>
+          <t>96413; 134297</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>94571; 142847</t>
+          <t>89228; 140463</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>130830; 175685</t>
+          <t>131283; 177910</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>232024; 290151</t>
+          <t>230977; 289120</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>157592; 210166</t>
+          <t>160915; 211198</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>166380; 224866</t>
+          <t>169275; 223476</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>64253; 97759</t>
+          <t>64733; 98549</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90092; 130510</t>
+          <t>88890; 130316</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>103578; 146830</t>
+          <t>103468; 146643</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>74930; 247129</t>
+          <t>78272; 249959</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>103267; 140029</t>
+          <t>101366; 139444</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>179037; 229038</t>
+          <t>179935; 228208</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>154027; 201767</t>
+          <t>152444; 200527</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>197282; 258458</t>
+          <t>198011; 258104</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>172733; 226490</t>
+          <t>174610; 230353</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>280588; 342096</t>
+          <t>280985; 344677</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>273684; 336053</t>
+          <t>268446; 332866</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>234569; 497320</t>
+          <t>252821; 498647</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>113179; 149848</t>
+          <t>112892; 150179</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>155109; 195914</t>
+          <t>154555; 196254</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>143576; 187962</t>
+          <t>145398; 188618</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>215319; 261655</t>
+          <t>217095; 258523</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>158826; 198566</t>
+          <t>159291; 199538</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>230861; 274497</t>
+          <t>231996; 273518</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>236076; 285474</t>
+          <t>236514; 285488</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>266524; 301408</t>
+          <t>264900; 301443</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>283510; 338021</t>
+          <t>284366; 336885</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>397912; 459898</t>
+          <t>397841; 457108</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>392476; 461569</t>
+          <t>395520; 461631</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>488829; 546344</t>
+          <t>491159; 548122</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>112699; 146951</t>
+          <t>115452; 147398</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>186966; 221819</t>
+          <t>187004; 222161</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>156239; 194099</t>
+          <t>156465; 193276</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>179159; 209511</t>
+          <t>179567; 211048</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>205591; 238025</t>
+          <t>206079; 239919</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>244245; 278084</t>
+          <t>242528; 277139</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>225091; 261368</t>
+          <t>225341; 261920</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>399999; 553912</t>
+          <t>398370; 547344</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>331097; 378604</t>
+          <t>330142; 376477</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>442993; 492055</t>
+          <t>442763; 489918</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>390929; 444570</t>
+          <t>391817; 444999</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>581849; 806115</t>
+          <t>581067; 810523</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>123309; 151170</t>
+          <t>124205; 152508</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>185353; 211557</t>
+          <t>185467; 212682</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>170445; 196977</t>
+          <t>171444; 197248</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>180911; 205486</t>
+          <t>179636; 205447</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>225704; 259886</t>
+          <t>228089; 262017</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>325542; 352420</t>
+          <t>326445; 352595</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>292667; 328568</t>
+          <t>293538; 330068</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>333922; 357335</t>
+          <t>333523; 356658</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>359645; 404229</t>
+          <t>362293; 402326</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>516815; 555848</t>
+          <t>519551; 559131</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>471459; 517213</t>
+          <t>471842; 516324</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>519847; 554594</t>
+          <t>520694; 555924</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>528509; 612482</t>
+          <t>528764; 612259</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>815615; 920105</t>
+          <t>813379; 919139</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>730904; 829383</t>
+          <t>728195; 826325</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>769346; 1057510</t>
+          <t>738827; 1054383</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>951145; 1064005</t>
+          <t>957519; 1062880</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1365655; 1482575</t>
+          <t>1364502; 1482274</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1172285; 1289757</t>
+          <t>1179342; 1295341</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1435776; 2015906</t>
+          <t>1433857; 1977414</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1510894; 1648760</t>
+          <t>1508901; 1646994</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2210371; 2375709</t>
+          <t>2212676; 2370765</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1937437; 2091778</t>
+          <t>1929719; 2086393</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2299674; 3002654</t>
+          <t>2316995; 2933743</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A_n_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A_n_R2-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,05</t>
+          <t>1,4; 4,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,46; 7,72</t>
+          <t>3,35; 7,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,45</t>
+          <t>1,99; 6,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,6; 14,65</t>
+          <t>5,5; 15,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,47; 13,82</t>
+          <t>8,44; 13,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,55; 19,65</t>
+          <t>12,52; 19,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,86; 14,81</t>
+          <t>8,24; 14,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,18; 19,4</t>
+          <t>9,96; 21,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,19; 8,39</t>
+          <t>5,27; 8,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,55; 12,58</t>
+          <t>8,75; 12,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,56; 9,46</t>
+          <t>5,59; 9,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,77; 15,47</t>
+          <t>9,06; 16,11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,35</t>
+          <t>2,44; 5,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,52; 12,19</t>
+          <t>7,74; 12,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,63; 10,51</t>
+          <t>5,91; 10,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,51; 17,04</t>
+          <t>8,68; 16,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,47; 17,42</t>
+          <t>11,35; 17,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,06; 24,29</t>
+          <t>16,95; 23,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,11; 17,89</t>
+          <t>11,67; 17,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,14; 20,86</t>
+          <t>14,23; 21,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,02; 10,0</t>
+          <t>7,04; 10,07</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,76; 16,84</t>
+          <t>12,83; 16,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,58; 13,14</t>
+          <t>9,42; 13,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,01; 17,47</t>
+          <t>12,65; 18,08</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,36; 10,73</t>
+          <t>6,66; 10,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,25; 15,4</t>
+          <t>10,29; 15,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,88; 12,69</t>
+          <t>7,93; 12,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,51; 17,47</t>
+          <t>11,16; 17,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,17; 17,34</t>
+          <t>11,89; 17,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,81; 27,45</t>
+          <t>21,07; 27,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,58; 20,31</t>
+          <t>14,68; 20,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,07; 23,73</t>
+          <t>19,27; 24,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,88; 13,39</t>
+          <t>9,82; 13,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,58; 20,76</t>
+          <t>16,49; 20,76</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,09; 15,87</t>
+          <t>12,01; 15,73</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,0; 19,81</t>
+          <t>15,93; 20,09</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,47; 18,98</t>
+          <t>12,09; 18,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,46; 21,2</t>
+          <t>14,64; 21,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,02; 22,7</t>
+          <t>15,95; 22,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,82; 28,16</t>
+          <t>23,24; 29,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,66; 27,04</t>
+          <t>19,79; 27,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,2; 37,03</t>
+          <t>29,56; 37,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,49; 30,89</t>
+          <t>23,9; 31,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,78; 36,21</t>
+          <t>30,78; 36,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,87; 22,26</t>
+          <t>17,03; 21,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,83; 28,0</t>
+          <t>22,74; 28,02</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,73; 25,7</t>
+          <t>21,14; 26,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,79; 31,15</t>
+          <t>28,11; 32,43</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,53%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>29,19; 38,83</t>
+          <t>29,64; 38,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35,99; 45,7</t>
+          <t>36,1; 46,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,42; 39,47</t>
+          <t>30,17; 39,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38,68; 46,06</t>
+          <t>37,42; 44,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>39,43; 49,39</t>
+          <t>39,21; 49,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,81; 61,08</t>
+          <t>51,9; 61,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,6; 57,46</t>
+          <t>47,7; 57,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>48,35; 55,02</t>
+          <t>48,67; 55,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>35,96; 42,61</t>
+          <t>36,07; 43,15</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45,35; 52,11</t>
+          <t>45,48; 52,43</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40,58; 47,36</t>
+          <t>40,5; 47,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>44,28; 49,42</t>
+          <t>44,01; 48,91</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>60,0%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39,46; 50,38</t>
+          <t>38,9; 50,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60,37; 71,71</t>
+          <t>60,99; 72,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46,8; 57,81</t>
+          <t>47,5; 58,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48,77; 57,32</t>
+          <t>48,41; 57,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>60,09; 69,96</t>
+          <t>59,96; 69,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68,51; 78,29</t>
+          <t>68,59; 78,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59,65; 69,33</t>
+          <t>58,96; 68,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>65,48; 89,97</t>
+          <t>63,76; 70,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>51,95; 59,24</t>
+          <t>51,66; 59,4</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>66,7; 73,81</t>
+          <t>66,91; 74,0</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55,02; 62,49</t>
+          <t>55,26; 62,66</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>59,5; 83,0</t>
+          <t>57,34; 62,79</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,56%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>59,18; 72,66</t>
+          <t>59,45; 72,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>74,23; 85,12</t>
+          <t>74,08; 84,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66,71; 76,75</t>
+          <t>66,6; 76,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63,53; 72,66</t>
+          <t>63,38; 72,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>68,31; 78,47</t>
+          <t>67,51; 77,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,92; 90,65</t>
+          <t>83,63; 90,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,35; 82,48</t>
+          <t>72,9; 82,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>78,32; 83,76</t>
+          <t>77,69; 83,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>66,62; 73,99</t>
+          <t>65,99; 73,85</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>81,33; 87,52</t>
+          <t>81,22; 87,07</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71,8; 78,57</t>
+          <t>71,55; 78,83</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73,48; 78,45</t>
+          <t>72,97; 78,14</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,14; 18,69</t>
+          <t>16,23; 18,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23,74; 26,82</t>
+          <t>23,61; 26,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21,45; 24,34</t>
+          <t>21,54; 24,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,35; 30,48</t>
+          <t>28,07; 31,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>28,34; 31,45</t>
+          <t>28,31; 31,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,35; 41,66</t>
+          <t>38,48; 41,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,27; 36,54</t>
+          <t>33,21; 36,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>38,62; 53,27</t>
+          <t>39,05; 41,92</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>22,67; 24,75</t>
+          <t>22,64; 24,8</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31,68; 33,94</t>
+          <t>31,65; 33,87</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27,81; 30,07</t>
+          <t>27,94; 30,08</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>32,31; 40,9</t>
+          <t>34,06; 36,27</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33796</t>
+          <t>38471</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42624</t>
+          <t>53799</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76419</t>
+          <t>92270</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6628; 20032</t>
+          <t>6910; 20963</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15714; 35045</t>
+          <t>15227; 34572</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9141; 27046</t>
+          <t>8342; 26506</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18397; 58586</t>
+          <t>22446; 61304</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>39583; 64615</t>
+          <t>39461; 65002</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54015; 84536</t>
+          <t>53846; 83778</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31096; 58628</t>
+          <t>32629; 57600</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28744; 60751</t>
+          <t>36099; 76382</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>49922; 80690</t>
+          <t>50704; 79542</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>75632; 111273</t>
+          <t>77423; 112461</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45294; 77087</t>
+          <t>45574; 76203</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>55393; 110336</t>
+          <t>69788; 124084</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51505</t>
+          <t>59823</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>84230</t>
+          <t>88453</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>135734</t>
+          <t>148276</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18568; 39367</t>
+          <t>17970; 37356</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51689; 83771</t>
+          <t>53161; 84276</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33234; 62085</t>
+          <t>34874; 59682</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36045; 72164</t>
+          <t>41399; 80875</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>71755; 108931</t>
+          <t>71025; 107506</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>104118; 148224</t>
+          <t>103413; 144079</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68272; 100801</t>
+          <t>65759; 99111</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51919; 106845</t>
+          <t>71417; 109368</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95597; 136149</t>
+          <t>95838; 137069</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>165491; 218484</t>
+          <t>166441; 220052</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>110589; 151601</t>
+          <t>108716; 152074</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>103010; 163451</t>
+          <t>123815; 176967</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77370</t>
+          <t>86715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>121025</t>
+          <t>136165</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>198394</t>
+          <t>222879</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>40612; 68498</t>
+          <t>42520; 68568</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>69890; 105011</t>
+          <t>70184; 106432</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>52746; 84917</t>
+          <t>53062; 84535</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61738; 93690</t>
+          <t>69288; 106018</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>83936; 119577</t>
+          <t>82010; 119887</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>147910; 195121</t>
+          <t>149754; 195417</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96413; 134297</t>
+          <t>97088; 135307</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>89228; 140463</t>
+          <t>120069; 155517</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>131283; 177910</t>
+          <t>130431; 177853</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>230977; 289120</t>
+          <t>229597; 289084</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>160915; 211198</t>
+          <t>159837; 209295</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>169275; 223476</t>
+          <t>198160; 249985</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>172157</t>
+          <t>186105</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>235686</t>
+          <t>248345</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>407843</t>
+          <t>434451</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>64733; 98549</t>
+          <t>62773; 96679</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>88890; 130316</t>
+          <t>89975; 129363</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>103468; 146643</t>
+          <t>103034; 144454</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>78272; 249959</t>
+          <t>162821; 209762</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>101366; 139444</t>
+          <t>102039; 139683</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>179935; 228208</t>
+          <t>182142; 228525</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>152444; 200527</t>
+          <t>155153; 201934</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>198011; 258104</t>
+          <t>226821; 269229</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>174610; 230353</t>
+          <t>176226; 225200</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>280985; 344677</t>
+          <t>279945; 344886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>268446; 332866</t>
+          <t>273799; 336784</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>252821; 498647</t>
+          <t>404075; 466144</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>236925</t>
+          <t>251065</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>283409</t>
+          <t>315746</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>520334</t>
+          <t>566811</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>112892; 150179</t>
+          <t>114608; 149332</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>154555; 196254</t>
+          <t>155022; 198421</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>145398; 188618</t>
+          <t>144166; 187567</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>217095; 258523</t>
+          <t>228027; 273939</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>159291; 199538</t>
+          <t>158416; 198725</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>231996; 273518</t>
+          <t>232407; 275992</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>236514; 285488</t>
+          <t>236984; 283666</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>264900; 301443</t>
+          <t>296308; 335769</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>284366; 336885</t>
+          <t>285184; 341169</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>397841; 457108</t>
+          <t>398930; 459943</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>395520; 461631</t>
+          <t>394828; 459123</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>491159; 548122</t>
+          <t>536155; 595808</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>196215</t>
+          <t>213729</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>474296</t>
+          <t>294050</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>670511</t>
+          <t>507779</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>115452; 147398</t>
+          <t>113816; 146438</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>187004; 222161</t>
+          <t>188944; 223900</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>156465; 193276</t>
+          <t>158813; 194631</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>179567; 211048</t>
+          <t>197068; 233000</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>206079; 239919</t>
+          <t>205613; 238786</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>242528; 277139</t>
+          <t>242811; 277035</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>225341; 261920</t>
+          <t>222711; 260569</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>398370; 547344</t>
+          <t>280010; 308574</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>330142; 376477</t>
+          <t>328338; 377510</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>442763; 489918</t>
+          <t>444151; 491220</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>391817; 444999</t>
+          <t>393476; 446177</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>581067; 810523</t>
+          <t>485203; 531344</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>193364</t>
+          <t>210655</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>345399</t>
+          <t>374768</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>538763</t>
+          <t>585423</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>124205; 152508</t>
+          <t>124782; 151151</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>185467; 212682</t>
+          <t>185096; 211287</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>171444; 197248</t>
+          <t>171155; 196339</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>179636; 205447</t>
+          <t>196610; 225999</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>228089; 262017</t>
+          <t>225411; 259411</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>326445; 352595</t>
+          <t>325300; 353616</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>293538; 330068</t>
+          <t>291721; 329562</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>333523; 356658</t>
+          <t>360941; 386822</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>362293; 402326</t>
+          <t>358862; 401570</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>519551; 559131</t>
+          <t>518835; 556255</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>471842; 516324</t>
+          <t>470226; 518029</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>520694; 555924</t>
+          <t>565339; 605423</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>961331</t>
+          <t>1046564</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1586668</t>
+          <t>1511326</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2547999</t>
+          <t>2557890</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>528764; 612259</t>
+          <t>531817; 613638</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>813379; 919139</t>
+          <t>809215; 914675</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>728195; 826325</t>
+          <t>731051; 828740</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>738827; 1054383</t>
+          <t>991785; 1110818</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>957519; 1062880</t>
+          <t>956577; 1067183</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1364502; 1482274</t>
+          <t>1369206; 1483275</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1179342; 1295341</t>
+          <t>1177292; 1295952</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1433857; 1977414</t>
+          <t>1459245; 1566536</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1508901; 1646994</t>
+          <t>1507175; 1650446</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2212676; 2370765</t>
+          <t>2210844; 2366137</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1929719; 2086393</t>
+          <t>1938917; 2087176</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2316995; 2933743</t>
+          <t>2475849; 2636790</t>
         </is>
       </c>
     </row>
